--- a/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>原子量是原子的什麼質量？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>總和</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>分子相對輕重</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>相對質量</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>比較值</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>原子量以哪個原子為基準？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>碳-12</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>標準</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>分子量是各原子量的？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>原子量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>總和</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>分子相對輕重</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>相加</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>莫耳是計量什麼的單位？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>分子相對輕重</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>粒子數量</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>總和</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>數量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>氫的原子量約為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>最小</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>氧的原子量約為？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>常用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>原子量有單位嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>沒有</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>原子量相加</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>分子相對輕重</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>總和</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>相對值</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>一打等於幾個？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>碳-12</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>12個</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>類比莫耳</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>分子量有沒有單位？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>沒有(相對值)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>CO₂(44&gt;18)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>移至高中,國中僅名詞認識</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>原子絕對質量極小不便,用比較</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>相對</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>碳-12被用作什麼的基準？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>原子量</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>原子量相加</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>總和</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>H₂O的分子量？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>1×2+16</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>CO₂的分子量？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>12+16×2</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>O₂的分子量？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>16×2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>分子量如何求得？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>粒子數量</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>分子相對輕重</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>原子量相加</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>計算</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>碳的原子量約？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>基準</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>CH₄的分子量？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>12+1×4</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>莫耳與質量是同類單位嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>原子量</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>相對質量</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>原子量相加</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>數量vs質量</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>NaCl的式量？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>58.5</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>23+35.5</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>H₂的分子量？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>1×2</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>CaCO₃的式量(Ca40 C12 O16)？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>58.5</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>40+12+48</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下1-3 原子量、分子量與莫耳　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>計算H₂SO₄的分子量(H1 S32 O16)？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>1×2+32+16×4</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何原子量用相對值？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>原子絕對質量極小不便,用比較</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>電子質量可忽略</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>用固定數量方便計量微粒</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>沒有(相對值)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>相對</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>分子量大小反映什麼？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>原子量</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>分子相對輕重</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>粒子數量</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>質量比較</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>Ca(OH)₂分子量(Ca40 O16 H1)？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>40+(16+1)×2</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>莫耳類比一打的用意？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>原子絕對質量極小不便,用比較</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>電子質量可忽略</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>用固定數量方便計量微粒</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>CO₂(44&gt;18)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>計量</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>C₆H₁₂O₆分子量(C12 H1 O16)？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>12×6+1×12+16×6</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>原子量約等於質量數因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>CO₂(44&gt;18)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>用固定數量方便計量微粒</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>電子質量可忽略</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>沒有(相對值)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>近似</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱此節不涉莫耳計算？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>沒有(相對值)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>移至高中,國中僅名詞認識</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>原子絕對質量極小不便,用比較</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>計量粒子數的單位(名詞)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>比較H₂O與CO₂分子量誰大？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>電子質量可忽略</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>原子絕對質量極小不便,用比較</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>用固定數量方便計量微粒</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>CO₂(44&gt;18)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>比較</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>莫耳在國中僅需認識為什麼？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>CO₂(44&gt;18)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>原子絕對質量極小不便,用比較</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>用固定數量方便計量微粒</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>計量粒子數的單位(名詞)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>名詞</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>比較值</t>
+          <t>比較值：原子太輕了沒辦法直接秤，所以用和某個原子比較後的相對數字來表示</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>標準</t>
+          <t>標準：科學家規定碳-12這種原子的質量剛好是12，其他原子都跟它比較大小</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>相加</t>
+          <t>相加：一個分子是由好幾個原子組成，把裡面每個原子的原子量全部加起來就是分子量</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>數量</t>
+          <t>數量：莫耳就像「打」一樣，是用來計算一大堆微小粒子（如原子、分子）個數的單位</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>最小</t>
+          <t>最小：氫原子是所有原子中最輕的，跟碳-12比起來，原子量大約只有1</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>常用</t>
+          <t>常用：氧原子的相對質量大約是16，是化學計算中很常用到的一個數字</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>相對值</t>
+          <t>相對值：因為原子量是用兩個原子相互比較出來的比值，比值本身是沒有單位的</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>類比莫耳</t>
+          <t>類比莫耳：一打是12個的意思，用來理解莫耳也是一種固定數量的計量方式</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>相對</t>
+          <t>相對：分子量是和碳-12相比較所得到的相對數值，本身沒有單位</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>基準</t>
+          <t>基準：科學家把碳-12的質量定為12，作為計算所有元素原子量的比較基準</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>1×2+16</t>
+          <t>1×2+16：水分子有2個氫（各1）和1個氧（16），加起來1乘2再加16等於18</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>12+16×2</t>
+          <t>12+16×2：二氧化碳有1個碳（12）和2個氧（各16），12加16乘2等於44</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>16×2</t>
+          <t>16×2：氧氣分子是由2個氧原子組成，16乘以2等於32</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>計算：把分子式中每一種原子的原子量，依照個數全部加總起來就是分子量</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>基準</t>
+          <t>基準：碳原子的原子量規定為12，是所有原子量比較時的參考基準</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>12+1×4</t>
+          <t>12+1×4：甲烷有1個碳（12）和4個氫（各1），12加1乘4等於16</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>數量vs質量</t>
+          <t>數量vs質量：莫耳是計算粒子有幾個的單位，克是秤重量的單位，兩者性質不同</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>23+35.5</t>
+          <t>23+35.5：食鹽是由1個鈉（23）和1個氯（35.5）組成，加起來等於58.5</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>1×2</t>
+          <t>1×2：氫原子量約為1，H₂分子含2個氫原子，1乘以2等於2</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>40+12+48</t>
+          <t>40+12+48：CaCO₃含1個鈣(40)、1個碳(12)、3個氧(16×3=48)，加總40+12+48等於100</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>1×2+32+16×4</t>
+          <t>1×2+32+16×4：2個氫共2、1個硫32、4個氧共64，2加32加64等於98</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相對</t>
+          <t>相對：一個原子輕到無法直接秤出公克數，用比較大小的方式紀錄反而方便又好用</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>質量比較</t>
+          <t>質量比較：分子量越大，代表這個分子相對來說越重，越小就代表越輕</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>40+(16+1)×2</t>
+          <t>40+(16+1)×2：1個鈣40，加上2組氫氧根各17（16加1），40加17乘2等於74</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>計量</t>
+          <t>計量：就像用「一打」代表12個雞蛋方便計數，莫耳也是用固定數量方便描述極多的微粒</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>12×6+1×12+16×6</t>
+          <t>12×6+1×12+16×6：6個碳72、12個氫12、6個氧96，加起來等於180</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>近似</t>
+          <t>近似：原子的質量幾乎都集中在質子和中子上，電子太輕了幾乎不影響原子量</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：國中階段只要先認識莫耳是計量單位的概念，實際換算會留到高中再學</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>比較</t>
+          <t>比較：H₂O分子量約為2+16=18，CO₂分子量約為12+32=44，所以CO₂的分子量比較大</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>名詞</t>
+          <t>名詞：國中階段對莫耳的要求只需要知道它是化學上用來計量大量微小粒子數目的一種單位名詞，不涉及莫耳的實際計算</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下1-3_三種難度測驗卷.xlsx
@@ -608,17 +608,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>58.5</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>100</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>碳-12</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>180</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>沒有</t>
+          <t>總和</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>原子量相加</t>
+          <t>相對質量</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>總和</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>74</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>總和</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>沒有</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>粒子數量</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>分子相對輕重</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>不是</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
